--- a/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/TrialBalancePrevYearExcel.xlsx
+++ b/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/TrialBalancePrevYearExcel.xlsx
@@ -1,89 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr hidePivotFieldList="1"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <x:workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.williams\Source\Gold\Yellowstone.Apps\Apps\W1\ExcelReports\app\ReportLayouts\Excel\GeneralLedger\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413957FC-2E07-46E3-B9E1-322F7D75289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="$TrialBalanceLCYPrint$" sheetId="17" r:id="rId1"/>
-    <sheet name="$TrialBalanceLCYAnalysis$" sheetId="12" r:id="rId2"/>
-    <sheet name="$TrialBalanceACYAnalysis$" sheetId="13" r:id="rId3"/>
-    <sheet name="TrialBalancePreviousYearData_Qu" sheetId="11" state="hidden" r:id="rId4"/>
-    <sheet name="$AboutTheReportLabel$" sheetId="16" r:id="rId5"/>
-    <sheet name="TrialBalancePreviousYearData" sheetId="5" state="hidden" r:id="rId6"/>
-    <sheet name="Dimension1" sheetId="6" state="hidden" r:id="rId7"/>
-    <sheet name="Dimension2" sheetId="7" state="hidden" r:id="rId8"/>
-    <sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId9"/>
-    <sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId10"/>
-    <sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId11"/>
-  </sheets>
-  <definedNames>
-    <definedName name="__">'$AboutTheReportLabel$'!$B$7</definedName>
-    <definedName name="DataRetrieved" localSheetId="4">#REF!</definedName>
-    <definedName name="DataRetrieved">#REF!</definedName>
-    <definedName name="DateFilter">_xlfn.XLOOKUP("DateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="ExternalData_1" localSheetId="3" hidden="1">TrialBalancePreviousYearData_Qu!$A$1:$AE$2</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" localSheetId="0">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" localSheetId="0">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="Slicer_AccountCategory">#N/A</definedName>
-    <definedName name="Slicer_AccountCategory1">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory1">#N/A</definedName>
-    <definedName name="Slicer_Dimension1Code">#N/A</definedName>
-    <definedName name="Slicer_Dimension1Code1">#N/A</definedName>
-    <definedName name="Slicer_Dimension2Code">#N/A</definedName>
-    <definedName name="Slicer_Dimension2Code1">#N/A</definedName>
-    <definedName name="TEMP" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",#REF!,#REF!,"none")</definedName>
-    <definedName name="TEMP2" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",#REF!,#REF!,"none")</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId12"/>
-  </pivotCaches>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+  <x:bookViews>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="$TrialBalanceLCYPrint$" sheetId="17" r:id="rId1"/>
+    <x:sheet name="$TrialBalanceLCYAnalysis$" sheetId="12" r:id="rId2"/>
+    <x:sheet name="$TrialBalanceACYAnalysis$" sheetId="13" r:id="rId3"/>
+    <x:sheet name="TrialBalancePreviousYearData_Qu" sheetId="11" state="hidden" r:id="rId4"/>
+    <x:sheet name="$AboutTheReportLabel$" sheetId="16" r:id="rId5"/>
+    <x:sheet name="TrialBalancePreviousYearData" sheetId="5" state="hidden" r:id="rId6"/>
+    <x:sheet name="Dimension1" sheetId="6" state="hidden" r:id="rId7"/>
+    <x:sheet name="Dimension2" sheetId="7" state="hidden" r:id="rId8"/>
+    <x:sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId9"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId10"/>
+    <x:sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId11"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="__">'$AboutTheReportLabel$'!$B$7</x:definedName>
+    <x:definedName name="DataRetrieved" localSheetId="4">#REF!</x:definedName>
+    <x:definedName name="DataRetrieved">#REF!</x:definedName>
+    <x:definedName name="DateFilter">_xlfn.XLOOKUP("DateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</x:definedName>
+    <x:definedName name="ExternalData_1" localSheetId="3" hidden="1">TrialBalancePreviousYearData_Qu!$A$1:$AE$2</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" localSheetId="0">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" localSheetId="0">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="Slicer_AccountCategory">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountCategory1">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2Code1">#N/A</x:definedName>
+    <x:definedName name="TEMP" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",#REF!,#REF!,"none")</x:definedName>
+    <x:definedName name="TEMP2" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",#REF!,#REF!,"none")</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="10" r:id="rId12"/>
+  </x:pivotCaches>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
@@ -94,11 +94,11 @@
         <x14:slicerCache r:id="rId19"/>
         <x14:slicerCache r:id="rId20"/>
       </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -108,9 +108,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6021,65 +6021,65 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="TrialBalancePreviousYearData" displayName="TrialBalancePreviousYearData" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="218" dataDxfId="217">
-  <autoFilter ref="A1:AE2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
-  <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Account" dataDxfId="216"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dimension1Code" dataDxfId="215"/>
-    <tableColumn id="3" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dimension2Code" dataDxfId="214"/>
-    <tableColumn id="4" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeDebit" dataDxfId="213"/>
-    <tableColumn id="5" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeCredit" dataDxfId="212"/>
-    <tableColumn id="6" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceDebit" dataDxfId="211"/>
-    <tableColumn id="7" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceCredit" dataDxfId="210"/>
-    <tableColumn id="8" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="LastPeriodNet" dataDxfId="209"/>
-    <tableColumn id="9" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="LastPeriodBalance" dataDxfId="208"/>
-    <tableColumn id="10" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetVariance" dataDxfId="207"/>
-    <tableColumn id="11" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetPercentVariance" dataDxfId="206"/>
-    <tableColumn id="12" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceVariance" dataDxfId="205"/>
-    <tableColumn id="13" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalancePercentVariance" dataDxfId="204"/>
-    <tableColumn id="14" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeDebitACY" dataDxfId="203"/>
-    <tableColumn id="15" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeCreditACY" dataDxfId="202"/>
-    <tableColumn id="16" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceDebitACY" dataDxfId="201"/>
-    <tableColumn id="17" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceCreditACY" dataDxfId="200"/>
-    <tableColumn id="18" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="LastPeriodNetACY" dataDxfId="199"/>
-    <tableColumn id="19" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="LastPeriodBalanceACY" dataDxfId="198"/>
-    <tableColumn id="20" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetVarianceACY" dataDxfId="197"/>
-    <tableColumn id="21" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetPercentVarianceACY" dataDxfId="196"/>
-    <tableColumn id="22" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceVarianceACY" dataDxfId="195"/>
-    <tableColumn id="23" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalancePercentVarianceACY" dataDxfId="194"/>
-    <tableColumn id="24" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountNumber" dataDxfId="193"/>
-    <tableColumn id="25" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountName" dataDxfId="192"/>
-    <tableColumn id="26" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="IncomeBalance" dataDxfId="191"/>
-    <tableColumn id="27" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountCategory" dataDxfId="190"/>
-    <tableColumn id="28" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountSubcategory" dataDxfId="189"/>
-    <tableColumn id="29" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountType" dataDxfId="188"/>
-    <tableColumn id="30" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Indentation" dataDxfId="187"/>
-    <tableColumn id="31" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="IndentedAccountName" dataDxfId="186"/>
-  </tableColumns>
-  <tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TrialBalancePreviousYearData" displayName="TrialBalancePreviousYearData" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="218" dataDxfId="217" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:AE2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+  <x:tableColumns count="31">
+    <x:tableColumn id="1" name="Account" dataDxfId="216" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dimension1Code" dataDxfId="215" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="3" name="Dimension2Code" dataDxfId="214" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="4" name="NetChangeDebit" dataDxfId="213" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="5" name="NetChangeCredit" dataDxfId="212" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="6" name="BalanceDebit" dataDxfId="211" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="7" name="BalanceCredit" dataDxfId="210" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="8" name="LastPeriodNet" dataDxfId="209" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="9" name="LastPeriodBalance" dataDxfId="208" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="10" name="NetVariance" dataDxfId="207" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="11" name="NetPercentVariance" dataDxfId="206" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="12" name="BalanceVariance" dataDxfId="205" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="13" name="BalancePercentVariance" dataDxfId="204" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="14" name="NetChangeDebitACY" dataDxfId="203" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="15" name="NetChangeCreditACY" dataDxfId="202" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="16" name="BalanceDebitACY" dataDxfId="201" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="17" name="BalanceCreditACY" dataDxfId="200" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="18" name="LastPeriodNetACY" dataDxfId="199" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="19" name="LastPeriodBalanceACY" dataDxfId="198" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="20" name="NetVarianceACY" dataDxfId="197" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="21" name="NetPercentVarianceACY" dataDxfId="196" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="22" name="BalanceVarianceACY" dataDxfId="195" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="23" name="BalancePercentVarianceACY" dataDxfId="194" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="24" name="AccountNumber" dataDxfId="193" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="25" name="AccountName" dataDxfId="192" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="26" name="IncomeBalance" dataDxfId="191" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="27" name="AccountCategory" dataDxfId="190" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="28" name="AccountSubcategory" dataDxfId="189" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="29" name="AccountType" dataDxfId="188" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="30" name="Indentation" dataDxfId="187" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="31" name="IndentedAccountName" dataDxfId="186" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="185">
-  <autoFilter ref="A1:B2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim1Code"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim1Name"/>
-  </tableColumns>
-  <tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="185" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim1Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dim1Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="184">
-  <autoFilter ref="A1:B2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim2Code"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim2Name"/>
-  </tableColumns>
-  <tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="184" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim2Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dim2Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="Table Style 1 CL" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
